--- a/sauce_test_case.xlsx
+++ b/sauce_test_case.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t xml:space="preserve">TC ID</t>
   </si>
@@ -61,13 +61,13 @@
     <t xml:space="preserve">Positive</t>
   </si>
   <si>
-    <t xml:space="preserve">Valid login with correct email and password</t>
+    <t xml:space="preserve">Login with all username</t>
   </si>
   <si>
     <t xml:space="preserve">User has registered account</t>
   </si>
   <si>
-    <t xml:space="preserve">Email: standard_user
+    <t xml:space="preserve">username: standard_user, locked_out_user, problem_user, performance_glitch_user, error_user, visual_user
 Password: secret_sauce</t>
   </si>
   <si>
@@ -75,32 +75,171 @@
 2. Enter valid email
 3. Enter valid password
 4. Click Log In
-5. Redirect to dashboard page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User successfully logs in and redirected to dashboard page</t>
+5. If login success, redirect to dashboard page. But, login failed show error message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User successfully logs in and redirected to dashboard page when username and password valid.But show error message when login failed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC002</t>
   </si>
   <si>
+    <t xml:space="preserve">Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check all list menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username: standard_user
+Password: secret_sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login
+2. Check all menu is clickable and have correct link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All menu clickable and have correct link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Reset App State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login
+2. Add some item to cart
+3. Click menu Reset App State
+4. Reload current page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All item in cart is reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add and remove item from cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login
+2. Add some item to cart. Check icon number of cart item increase.
+3. Remove all item from cart. Check icon number of cart item decrease.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon number of cart increase or decrease base on item cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkout item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login
+2. Add item to cart
+3. Checkout, check information and detal checkout is correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail checkout is correct and item is checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Negative</t>
   </si>
   <si>
-    <t xml:space="preserve">Invalid password</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email: registered@test.com
-Password: Wrong123!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open login page
+    <t xml:space="preserve">Wrong password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username: standard_user
+Password: wr0ngP4ssword!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open login page https://www.saucedemo.com/
 2. Enter valid email
 3. Enter wrong password
-4. Click Log In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validation message displayed and login fails</t>
+4. Login fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login failed and error message is show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQL Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username: standard_user
+Password:  ' OR 1=1--</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open login page https://www.saucedemo.com/
+2. Enter valid email
+3. Enter wrong password ( OR 1=1--)
+4. Login fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XSS Attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username: standard_user
+Password:  &lt;script&gt;alert(1)&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open login page https://www.saucedemo.com/
+2. Enter valid email
+3. Enter wrong password (&lt;script&gt;alert(1)&lt;/script&gt;)
+4. Login fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email or password empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username: 
+Password: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open login page https://www.saucedemo.com/
+2. Enter empty email or empty password
+3. Login fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login
+2. Logout
+3. Direct access to link https://www.saucedemo.com/inventory.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory menu failed to open and error message is show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC011</t>
   </si>
 </sst>
 </file>
@@ -110,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -132,6 +271,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,17 +321,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -197,8 +338,8 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -218,7 +359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ15"/>
+  <dimension ref="A1:AMJ26"/>
   <sheetFormatPr defaultColWidth="8.4296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.43"/>
@@ -228,47 +369,46 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="54.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1020" min="10" style="1" width="8.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1021" min="1021" style="2" width="8.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="2" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="59.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1021" min="10" style="1" width="8.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AMG1" s="2"/>
-      <c r="AMH1" s="2"/>
-      <c r="AMI1" s="2"/>
-      <c r="AMJ1" s="2"/>
+      <c r="AMG1" s="1"/>
+      <c r="AMH1" s="1"/>
+      <c r="AMI1" s="1"/>
+      <c r="AMJ1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="65.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="142.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -297,170 +437,1346 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="68.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="3" customFormat="true" ht="68.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="63.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0"/>
-      <c r="B4" s="0"/>
-      <c r="C4" s="0"/>
-      <c r="D4" s="0"/>
-      <c r="E4" s="0"/>
-      <c r="F4" s="0"/>
-      <c r="G4" s="0"/>
-      <c r="H4" s="0"/>
-      <c r="I4" s="0"/>
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="50.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0"/>
-      <c r="B5" s="0"/>
-      <c r="C5" s="0"/>
-      <c r="D5" s="0"/>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
+      <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
+    <row r="6" customFormat="false" ht="73.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0"/>
-      <c r="B7" s="0"/>
-      <c r="C7" s="0"/>
-      <c r="D7" s="0"/>
-      <c r="E7" s="0"/>
-      <c r="F7" s="0"/>
-      <c r="G7" s="0"/>
-      <c r="H7" s="0"/>
-      <c r="I7" s="0"/>
+    <row r="7" customFormat="false" ht="104.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-      <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
-      <c r="E8" s="0"/>
-      <c r="F8" s="0"/>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-      <c r="I8" s="0"/>
+    <row r="8" customFormat="false" ht="78.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
-      <c r="C9" s="0"/>
-      <c r="D9" s="0"/>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-      <c r="I9" s="0"/>
+    <row r="9" customFormat="false" ht="59.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0"/>
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-      <c r="I10" s="0"/>
+    <row r="10" customFormat="false" ht="72.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="11" s="4" customFormat="true" ht="51.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="AMG11" s="5"/>
-      <c r="AMH11" s="5"/>
-      <c r="AMI11" s="5"/>
-      <c r="AMJ11" s="5"/>
+    <row r="11" s="3" customFormat="true" ht="51.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
+      <c r="A12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
-      <c r="I14" s="0"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="11" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+      <c r="G26" s="0"/>
+      <c r="H26" s="0"/>
+      <c r="I26" s="0"/>
+      <c r="J26" s="0"/>
+      <c r="K26" s="0"/>
+      <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+      <c r="O26" s="0"/>
+      <c r="P26" s="0"/>
+      <c r="Q26" s="0"/>
+      <c r="R26" s="0"/>
+      <c r="S26" s="0"/>
+      <c r="T26" s="0"/>
+      <c r="U26" s="0"/>
+      <c r="V26" s="0"/>
+      <c r="W26" s="0"/>
+      <c r="X26" s="0"/>
+      <c r="Y26" s="0"/>
+      <c r="Z26" s="0"/>
+      <c r="AA26" s="0"/>
+      <c r="AB26" s="0"/>
+      <c r="AC26" s="0"/>
+      <c r="AD26" s="0"/>
+      <c r="AE26" s="0"/>
+      <c r="AF26" s="0"/>
+      <c r="AG26" s="0"/>
+      <c r="AH26" s="0"/>
+      <c r="AI26" s="0"/>
+      <c r="AJ26" s="0"/>
+      <c r="AK26" s="0"/>
+      <c r="AL26" s="0"/>
+      <c r="AM26" s="0"/>
+      <c r="AN26" s="0"/>
+      <c r="AO26" s="0"/>
+      <c r="AP26" s="0"/>
+      <c r="AQ26" s="0"/>
+      <c r="AR26" s="0"/>
+      <c r="AS26" s="0"/>
+      <c r="AT26" s="0"/>
+      <c r="AU26" s="0"/>
+      <c r="AV26" s="0"/>
+      <c r="AW26" s="0"/>
+      <c r="AX26" s="0"/>
+      <c r="AY26" s="0"/>
+      <c r="AZ26" s="0"/>
+      <c r="BA26" s="0"/>
+      <c r="BB26" s="0"/>
+      <c r="BC26" s="0"/>
+      <c r="BD26" s="0"/>
+      <c r="BE26" s="0"/>
+      <c r="BF26" s="0"/>
+      <c r="BG26" s="0"/>
+      <c r="BH26" s="0"/>
+      <c r="BI26" s="0"/>
+      <c r="BJ26" s="0"/>
+      <c r="BK26" s="0"/>
+      <c r="BL26" s="0"/>
+      <c r="BM26" s="0"/>
+      <c r="BN26" s="0"/>
+      <c r="BO26" s="0"/>
+      <c r="BP26" s="0"/>
+      <c r="BQ26" s="0"/>
+      <c r="BR26" s="0"/>
+      <c r="BS26" s="0"/>
+      <c r="BT26" s="0"/>
+      <c r="BU26" s="0"/>
+      <c r="BV26" s="0"/>
+      <c r="BW26" s="0"/>
+      <c r="BX26" s="0"/>
+      <c r="BY26" s="0"/>
+      <c r="BZ26" s="0"/>
+      <c r="CA26" s="0"/>
+      <c r="CB26" s="0"/>
+      <c r="CC26" s="0"/>
+      <c r="CD26" s="0"/>
+      <c r="CE26" s="0"/>
+      <c r="CF26" s="0"/>
+      <c r="CG26" s="0"/>
+      <c r="CH26" s="0"/>
+      <c r="CI26" s="0"/>
+      <c r="CJ26" s="0"/>
+      <c r="CK26" s="0"/>
+      <c r="CL26" s="0"/>
+      <c r="CM26" s="0"/>
+      <c r="CN26" s="0"/>
+      <c r="CO26" s="0"/>
+      <c r="CP26" s="0"/>
+      <c r="CQ26" s="0"/>
+      <c r="CR26" s="0"/>
+      <c r="CS26" s="0"/>
+      <c r="CT26" s="0"/>
+      <c r="CU26" s="0"/>
+      <c r="CV26" s="0"/>
+      <c r="CW26" s="0"/>
+      <c r="CX26" s="0"/>
+      <c r="CY26" s="0"/>
+      <c r="CZ26" s="0"/>
+      <c r="DA26" s="0"/>
+      <c r="DB26" s="0"/>
+      <c r="DC26" s="0"/>
+      <c r="DD26" s="0"/>
+      <c r="DE26" s="0"/>
+      <c r="DF26" s="0"/>
+      <c r="DG26" s="0"/>
+      <c r="DH26" s="0"/>
+      <c r="DI26" s="0"/>
+      <c r="DJ26" s="0"/>
+      <c r="DK26" s="0"/>
+      <c r="DL26" s="0"/>
+      <c r="DM26" s="0"/>
+      <c r="DN26" s="0"/>
+      <c r="DO26" s="0"/>
+      <c r="DP26" s="0"/>
+      <c r="DQ26" s="0"/>
+      <c r="DR26" s="0"/>
+      <c r="DS26" s="0"/>
+      <c r="DT26" s="0"/>
+      <c r="DU26" s="0"/>
+      <c r="DV26" s="0"/>
+      <c r="DW26" s="0"/>
+      <c r="DX26" s="0"/>
+      <c r="DY26" s="0"/>
+      <c r="DZ26" s="0"/>
+      <c r="EA26" s="0"/>
+      <c r="EB26" s="0"/>
+      <c r="EC26" s="0"/>
+      <c r="ED26" s="0"/>
+      <c r="EE26" s="0"/>
+      <c r="EF26" s="0"/>
+      <c r="EG26" s="0"/>
+      <c r="EH26" s="0"/>
+      <c r="EI26" s="0"/>
+      <c r="EJ26" s="0"/>
+      <c r="EK26" s="0"/>
+      <c r="EL26" s="0"/>
+      <c r="EM26" s="0"/>
+      <c r="EN26" s="0"/>
+      <c r="EO26" s="0"/>
+      <c r="EP26" s="0"/>
+      <c r="EQ26" s="0"/>
+      <c r="ER26" s="0"/>
+      <c r="ES26" s="0"/>
+      <c r="ET26" s="0"/>
+      <c r="EU26" s="0"/>
+      <c r="EV26" s="0"/>
+      <c r="EW26" s="0"/>
+      <c r="EX26" s="0"/>
+      <c r="EY26" s="0"/>
+      <c r="EZ26" s="0"/>
+      <c r="FA26" s="0"/>
+      <c r="FB26" s="0"/>
+      <c r="FC26" s="0"/>
+      <c r="FD26" s="0"/>
+      <c r="FE26" s="0"/>
+      <c r="FF26" s="0"/>
+      <c r="FG26" s="0"/>
+      <c r="FH26" s="0"/>
+      <c r="FI26" s="0"/>
+      <c r="FJ26" s="0"/>
+      <c r="FK26" s="0"/>
+      <c r="FL26" s="0"/>
+      <c r="FM26" s="0"/>
+      <c r="FN26" s="0"/>
+      <c r="FO26" s="0"/>
+      <c r="FP26" s="0"/>
+      <c r="FQ26" s="0"/>
+      <c r="FR26" s="0"/>
+      <c r="FS26" s="0"/>
+      <c r="FT26" s="0"/>
+      <c r="FU26" s="0"/>
+      <c r="FV26" s="0"/>
+      <c r="FW26" s="0"/>
+      <c r="FX26" s="0"/>
+      <c r="FY26" s="0"/>
+      <c r="FZ26" s="0"/>
+      <c r="GA26" s="0"/>
+      <c r="GB26" s="0"/>
+      <c r="GC26" s="0"/>
+      <c r="GD26" s="0"/>
+      <c r="GE26" s="0"/>
+      <c r="GF26" s="0"/>
+      <c r="GG26" s="0"/>
+      <c r="GH26" s="0"/>
+      <c r="GI26" s="0"/>
+      <c r="GJ26" s="0"/>
+      <c r="GK26" s="0"/>
+      <c r="GL26" s="0"/>
+      <c r="GM26" s="0"/>
+      <c r="GN26" s="0"/>
+      <c r="GO26" s="0"/>
+      <c r="GP26" s="0"/>
+      <c r="GQ26" s="0"/>
+      <c r="GR26" s="0"/>
+      <c r="GS26" s="0"/>
+      <c r="GT26" s="0"/>
+      <c r="GU26" s="0"/>
+      <c r="GV26" s="0"/>
+      <c r="GW26" s="0"/>
+      <c r="GX26" s="0"/>
+      <c r="GY26" s="0"/>
+      <c r="GZ26" s="0"/>
+      <c r="HA26" s="0"/>
+      <c r="HB26" s="0"/>
+      <c r="HC26" s="0"/>
+      <c r="HD26" s="0"/>
+      <c r="HE26" s="0"/>
+      <c r="HF26" s="0"/>
+      <c r="HG26" s="0"/>
+      <c r="HH26" s="0"/>
+      <c r="HI26" s="0"/>
+      <c r="HJ26" s="0"/>
+      <c r="HK26" s="0"/>
+      <c r="HL26" s="0"/>
+      <c r="HM26" s="0"/>
+      <c r="HN26" s="0"/>
+      <c r="HO26" s="0"/>
+      <c r="HP26" s="0"/>
+      <c r="HQ26" s="0"/>
+      <c r="HR26" s="0"/>
+      <c r="HS26" s="0"/>
+      <c r="HT26" s="0"/>
+      <c r="HU26" s="0"/>
+      <c r="HV26" s="0"/>
+      <c r="HW26" s="0"/>
+      <c r="HX26" s="0"/>
+      <c r="HY26" s="0"/>
+      <c r="HZ26" s="0"/>
+      <c r="IA26" s="0"/>
+      <c r="IB26" s="0"/>
+      <c r="IC26" s="0"/>
+      <c r="ID26" s="0"/>
+      <c r="IE26" s="0"/>
+      <c r="IF26" s="0"/>
+      <c r="IG26" s="0"/>
+      <c r="IH26" s="0"/>
+      <c r="II26" s="0"/>
+      <c r="IJ26" s="0"/>
+      <c r="IK26" s="0"/>
+      <c r="IL26" s="0"/>
+      <c r="IM26" s="0"/>
+      <c r="IN26" s="0"/>
+      <c r="IO26" s="0"/>
+      <c r="IP26" s="0"/>
+      <c r="IQ26" s="0"/>
+      <c r="IR26" s="0"/>
+      <c r="IS26" s="0"/>
+      <c r="IT26" s="0"/>
+      <c r="IU26" s="0"/>
+      <c r="IV26" s="0"/>
+      <c r="IW26" s="0"/>
+      <c r="IX26" s="0"/>
+      <c r="IY26" s="0"/>
+      <c r="IZ26" s="0"/>
+      <c r="JA26" s="0"/>
+      <c r="JB26" s="0"/>
+      <c r="JC26" s="0"/>
+      <c r="JD26" s="0"/>
+      <c r="JE26" s="0"/>
+      <c r="JF26" s="0"/>
+      <c r="JG26" s="0"/>
+      <c r="JH26" s="0"/>
+      <c r="JI26" s="0"/>
+      <c r="JJ26" s="0"/>
+      <c r="JK26" s="0"/>
+      <c r="JL26" s="0"/>
+      <c r="JM26" s="0"/>
+      <c r="JN26" s="0"/>
+      <c r="JO26" s="0"/>
+      <c r="JP26" s="0"/>
+      <c r="JQ26" s="0"/>
+      <c r="JR26" s="0"/>
+      <c r="JS26" s="0"/>
+      <c r="JT26" s="0"/>
+      <c r="JU26" s="0"/>
+      <c r="JV26" s="0"/>
+      <c r="JW26" s="0"/>
+      <c r="JX26" s="0"/>
+      <c r="JY26" s="0"/>
+      <c r="JZ26" s="0"/>
+      <c r="KA26" s="0"/>
+      <c r="KB26" s="0"/>
+      <c r="KC26" s="0"/>
+      <c r="KD26" s="0"/>
+      <c r="KE26" s="0"/>
+      <c r="KF26" s="0"/>
+      <c r="KG26" s="0"/>
+      <c r="KH26" s="0"/>
+      <c r="KI26" s="0"/>
+      <c r="KJ26" s="0"/>
+      <c r="KK26" s="0"/>
+      <c r="KL26" s="0"/>
+      <c r="KM26" s="0"/>
+      <c r="KN26" s="0"/>
+      <c r="KO26" s="0"/>
+      <c r="KP26" s="0"/>
+      <c r="KQ26" s="0"/>
+      <c r="KR26" s="0"/>
+      <c r="KS26" s="0"/>
+      <c r="KT26" s="0"/>
+      <c r="KU26" s="0"/>
+      <c r="KV26" s="0"/>
+      <c r="KW26" s="0"/>
+      <c r="KX26" s="0"/>
+      <c r="KY26" s="0"/>
+      <c r="KZ26" s="0"/>
+      <c r="LA26" s="0"/>
+      <c r="LB26" s="0"/>
+      <c r="LC26" s="0"/>
+      <c r="LD26" s="0"/>
+      <c r="LE26" s="0"/>
+      <c r="LF26" s="0"/>
+      <c r="LG26" s="0"/>
+      <c r="LH26" s="0"/>
+      <c r="LI26" s="0"/>
+      <c r="LJ26" s="0"/>
+      <c r="LK26" s="0"/>
+      <c r="LL26" s="0"/>
+      <c r="LM26" s="0"/>
+      <c r="LN26" s="0"/>
+      <c r="LO26" s="0"/>
+      <c r="LP26" s="0"/>
+      <c r="LQ26" s="0"/>
+      <c r="LR26" s="0"/>
+      <c r="LS26" s="0"/>
+      <c r="LT26" s="0"/>
+      <c r="LU26" s="0"/>
+      <c r="LV26" s="0"/>
+      <c r="LW26" s="0"/>
+      <c r="LX26" s="0"/>
+      <c r="LY26" s="0"/>
+      <c r="LZ26" s="0"/>
+      <c r="MA26" s="0"/>
+      <c r="MB26" s="0"/>
+      <c r="MC26" s="0"/>
+      <c r="MD26" s="0"/>
+      <c r="ME26" s="0"/>
+      <c r="MF26" s="0"/>
+      <c r="MG26" s="0"/>
+      <c r="MH26" s="0"/>
+      <c r="MI26" s="0"/>
+      <c r="MJ26" s="0"/>
+      <c r="MK26" s="0"/>
+      <c r="ML26" s="0"/>
+      <c r="MM26" s="0"/>
+      <c r="MN26" s="0"/>
+      <c r="MO26" s="0"/>
+      <c r="MP26" s="0"/>
+      <c r="MQ26" s="0"/>
+      <c r="MR26" s="0"/>
+      <c r="MS26" s="0"/>
+      <c r="MT26" s="0"/>
+      <c r="MU26" s="0"/>
+      <c r="MV26" s="0"/>
+      <c r="MW26" s="0"/>
+      <c r="MX26" s="0"/>
+      <c r="MY26" s="0"/>
+      <c r="MZ26" s="0"/>
+      <c r="NA26" s="0"/>
+      <c r="NB26" s="0"/>
+      <c r="NC26" s="0"/>
+      <c r="ND26" s="0"/>
+      <c r="NE26" s="0"/>
+      <c r="NF26" s="0"/>
+      <c r="NG26" s="0"/>
+      <c r="NH26" s="0"/>
+      <c r="NI26" s="0"/>
+      <c r="NJ26" s="0"/>
+      <c r="NK26" s="0"/>
+      <c r="NL26" s="0"/>
+      <c r="NM26" s="0"/>
+      <c r="NN26" s="0"/>
+      <c r="NO26" s="0"/>
+      <c r="NP26" s="0"/>
+      <c r="NQ26" s="0"/>
+      <c r="NR26" s="0"/>
+      <c r="NS26" s="0"/>
+      <c r="NT26" s="0"/>
+      <c r="NU26" s="0"/>
+      <c r="NV26" s="0"/>
+      <c r="NW26" s="0"/>
+      <c r="NX26" s="0"/>
+      <c r="NY26" s="0"/>
+      <c r="NZ26" s="0"/>
+      <c r="OA26" s="0"/>
+      <c r="OB26" s="0"/>
+      <c r="OC26" s="0"/>
+      <c r="OD26" s="0"/>
+      <c r="OE26" s="0"/>
+      <c r="OF26" s="0"/>
+      <c r="OG26" s="0"/>
+      <c r="OH26" s="0"/>
+      <c r="OI26" s="0"/>
+      <c r="OJ26" s="0"/>
+      <c r="OK26" s="0"/>
+      <c r="OL26" s="0"/>
+      <c r="OM26" s="0"/>
+      <c r="ON26" s="0"/>
+      <c r="OO26" s="0"/>
+      <c r="OP26" s="0"/>
+      <c r="OQ26" s="0"/>
+      <c r="OR26" s="0"/>
+      <c r="OS26" s="0"/>
+      <c r="OT26" s="0"/>
+      <c r="OU26" s="0"/>
+      <c r="OV26" s="0"/>
+      <c r="OW26" s="0"/>
+      <c r="OX26" s="0"/>
+      <c r="OY26" s="0"/>
+      <c r="OZ26" s="0"/>
+      <c r="PA26" s="0"/>
+      <c r="PB26" s="0"/>
+      <c r="PC26" s="0"/>
+      <c r="PD26" s="0"/>
+      <c r="PE26" s="0"/>
+      <c r="PF26" s="0"/>
+      <c r="PG26" s="0"/>
+      <c r="PH26" s="0"/>
+      <c r="PI26" s="0"/>
+      <c r="PJ26" s="0"/>
+      <c r="PK26" s="0"/>
+      <c r="PL26" s="0"/>
+      <c r="PM26" s="0"/>
+      <c r="PN26" s="0"/>
+      <c r="PO26" s="0"/>
+      <c r="PP26" s="0"/>
+      <c r="PQ26" s="0"/>
+      <c r="PR26" s="0"/>
+      <c r="PS26" s="0"/>
+      <c r="PT26" s="0"/>
+      <c r="PU26" s="0"/>
+      <c r="PV26" s="0"/>
+      <c r="PW26" s="0"/>
+      <c r="PX26" s="0"/>
+      <c r="PY26" s="0"/>
+      <c r="PZ26" s="0"/>
+      <c r="QA26" s="0"/>
+      <c r="QB26" s="0"/>
+      <c r="QC26" s="0"/>
+      <c r="QD26" s="0"/>
+      <c r="QE26" s="0"/>
+      <c r="QF26" s="0"/>
+      <c r="QG26" s="0"/>
+      <c r="QH26" s="0"/>
+      <c r="QI26" s="0"/>
+      <c r="QJ26" s="0"/>
+      <c r="QK26" s="0"/>
+      <c r="QL26" s="0"/>
+      <c r="QM26" s="0"/>
+      <c r="QN26" s="0"/>
+      <c r="QO26" s="0"/>
+      <c r="QP26" s="0"/>
+      <c r="QQ26" s="0"/>
+      <c r="QR26" s="0"/>
+      <c r="QS26" s="0"/>
+      <c r="QT26" s="0"/>
+      <c r="QU26" s="0"/>
+      <c r="QV26" s="0"/>
+      <c r="QW26" s="0"/>
+      <c r="QX26" s="0"/>
+      <c r="QY26" s="0"/>
+      <c r="QZ26" s="0"/>
+      <c r="RA26" s="0"/>
+      <c r="RB26" s="0"/>
+      <c r="RC26" s="0"/>
+      <c r="RD26" s="0"/>
+      <c r="RE26" s="0"/>
+      <c r="RF26" s="0"/>
+      <c r="RG26" s="0"/>
+      <c r="RH26" s="0"/>
+      <c r="RI26" s="0"/>
+      <c r="RJ26" s="0"/>
+      <c r="RK26" s="0"/>
+      <c r="RL26" s="0"/>
+      <c r="RM26" s="0"/>
+      <c r="RN26" s="0"/>
+      <c r="RO26" s="0"/>
+      <c r="RP26" s="0"/>
+      <c r="RQ26" s="0"/>
+      <c r="RR26" s="0"/>
+      <c r="RS26" s="0"/>
+      <c r="RT26" s="0"/>
+      <c r="RU26" s="0"/>
+      <c r="RV26" s="0"/>
+      <c r="RW26" s="0"/>
+      <c r="RX26" s="0"/>
+      <c r="RY26" s="0"/>
+      <c r="RZ26" s="0"/>
+      <c r="SA26" s="0"/>
+      <c r="SB26" s="0"/>
+      <c r="SC26" s="0"/>
+      <c r="SD26" s="0"/>
+      <c r="SE26" s="0"/>
+      <c r="SF26" s="0"/>
+      <c r="SG26" s="0"/>
+      <c r="SH26" s="0"/>
+      <c r="SI26" s="0"/>
+      <c r="SJ26" s="0"/>
+      <c r="SK26" s="0"/>
+      <c r="SL26" s="0"/>
+      <c r="SM26" s="0"/>
+      <c r="SN26" s="0"/>
+      <c r="SO26" s="0"/>
+      <c r="SP26" s="0"/>
+      <c r="SQ26" s="0"/>
+      <c r="SR26" s="0"/>
+      <c r="SS26" s="0"/>
+      <c r="ST26" s="0"/>
+      <c r="SU26" s="0"/>
+      <c r="SV26" s="0"/>
+      <c r="SW26" s="0"/>
+      <c r="SX26" s="0"/>
+      <c r="SY26" s="0"/>
+      <c r="SZ26" s="0"/>
+      <c r="TA26" s="0"/>
+      <c r="TB26" s="0"/>
+      <c r="TC26" s="0"/>
+      <c r="TD26" s="0"/>
+      <c r="TE26" s="0"/>
+      <c r="TF26" s="0"/>
+      <c r="TG26" s="0"/>
+      <c r="TH26" s="0"/>
+      <c r="TI26" s="0"/>
+      <c r="TJ26" s="0"/>
+      <c r="TK26" s="0"/>
+      <c r="TL26" s="0"/>
+      <c r="TM26" s="0"/>
+      <c r="TN26" s="0"/>
+      <c r="TO26" s="0"/>
+      <c r="TP26" s="0"/>
+      <c r="TQ26" s="0"/>
+      <c r="TR26" s="0"/>
+      <c r="TS26" s="0"/>
+      <c r="TT26" s="0"/>
+      <c r="TU26" s="0"/>
+      <c r="TV26" s="0"/>
+      <c r="TW26" s="0"/>
+      <c r="TX26" s="0"/>
+      <c r="TY26" s="0"/>
+      <c r="TZ26" s="0"/>
+      <c r="UA26" s="0"/>
+      <c r="UB26" s="0"/>
+      <c r="UC26" s="0"/>
+      <c r="UD26" s="0"/>
+      <c r="UE26" s="0"/>
+      <c r="UF26" s="0"/>
+      <c r="UG26" s="0"/>
+      <c r="UH26" s="0"/>
+      <c r="UI26" s="0"/>
+      <c r="UJ26" s="0"/>
+      <c r="UK26" s="0"/>
+      <c r="UL26" s="0"/>
+      <c r="UM26" s="0"/>
+      <c r="UN26" s="0"/>
+      <c r="UO26" s="0"/>
+      <c r="UP26" s="0"/>
+      <c r="UQ26" s="0"/>
+      <c r="UR26" s="0"/>
+      <c r="US26" s="0"/>
+      <c r="UT26" s="0"/>
+      <c r="UU26" s="0"/>
+      <c r="UV26" s="0"/>
+      <c r="UW26" s="0"/>
+      <c r="UX26" s="0"/>
+      <c r="UY26" s="0"/>
+      <c r="UZ26" s="0"/>
+      <c r="VA26" s="0"/>
+      <c r="VB26" s="0"/>
+      <c r="VC26" s="0"/>
+      <c r="VD26" s="0"/>
+      <c r="VE26" s="0"/>
+      <c r="VF26" s="0"/>
+      <c r="VG26" s="0"/>
+      <c r="VH26" s="0"/>
+      <c r="VI26" s="0"/>
+      <c r="VJ26" s="0"/>
+      <c r="VK26" s="0"/>
+      <c r="VL26" s="0"/>
+      <c r="VM26" s="0"/>
+      <c r="VN26" s="0"/>
+      <c r="VO26" s="0"/>
+      <c r="VP26" s="0"/>
+      <c r="VQ26" s="0"/>
+      <c r="VR26" s="0"/>
+      <c r="VS26" s="0"/>
+      <c r="VT26" s="0"/>
+      <c r="VU26" s="0"/>
+      <c r="VV26" s="0"/>
+      <c r="VW26" s="0"/>
+      <c r="VX26" s="0"/>
+      <c r="VY26" s="0"/>
+      <c r="VZ26" s="0"/>
+      <c r="WA26" s="0"/>
+      <c r="WB26" s="0"/>
+      <c r="WC26" s="0"/>
+      <c r="WD26" s="0"/>
+      <c r="WE26" s="0"/>
+      <c r="WF26" s="0"/>
+      <c r="WG26" s="0"/>
+      <c r="WH26" s="0"/>
+      <c r="WI26" s="0"/>
+      <c r="WJ26" s="0"/>
+      <c r="WK26" s="0"/>
+      <c r="WL26" s="0"/>
+      <c r="WM26" s="0"/>
+      <c r="WN26" s="0"/>
+      <c r="WO26" s="0"/>
+      <c r="WP26" s="0"/>
+      <c r="WQ26" s="0"/>
+      <c r="WR26" s="0"/>
+      <c r="WS26" s="0"/>
+      <c r="WT26" s="0"/>
+      <c r="WU26" s="0"/>
+      <c r="WV26" s="0"/>
+      <c r="WW26" s="0"/>
+      <c r="WX26" s="0"/>
+      <c r="WY26" s="0"/>
+      <c r="WZ26" s="0"/>
+      <c r="XA26" s="0"/>
+      <c r="XB26" s="0"/>
+      <c r="XC26" s="0"/>
+      <c r="XD26" s="0"/>
+      <c r="XE26" s="0"/>
+      <c r="XF26" s="0"/>
+      <c r="XG26" s="0"/>
+      <c r="XH26" s="0"/>
+      <c r="XI26" s="0"/>
+      <c r="XJ26" s="0"/>
+      <c r="XK26" s="0"/>
+      <c r="XL26" s="0"/>
+      <c r="XM26" s="0"/>
+      <c r="XN26" s="0"/>
+      <c r="XO26" s="0"/>
+      <c r="XP26" s="0"/>
+      <c r="XQ26" s="0"/>
+      <c r="XR26" s="0"/>
+      <c r="XS26" s="0"/>
+      <c r="XT26" s="0"/>
+      <c r="XU26" s="0"/>
+      <c r="XV26" s="0"/>
+      <c r="XW26" s="0"/>
+      <c r="XX26" s="0"/>
+      <c r="XY26" s="0"/>
+      <c r="XZ26" s="0"/>
+      <c r="YA26" s="0"/>
+      <c r="YB26" s="0"/>
+      <c r="YC26" s="0"/>
+      <c r="YD26" s="0"/>
+      <c r="YE26" s="0"/>
+      <c r="YF26" s="0"/>
+      <c r="YG26" s="0"/>
+      <c r="YH26" s="0"/>
+      <c r="YI26" s="0"/>
+      <c r="YJ26" s="0"/>
+      <c r="YK26" s="0"/>
+      <c r="YL26" s="0"/>
+      <c r="YM26" s="0"/>
+      <c r="YN26" s="0"/>
+      <c r="YO26" s="0"/>
+      <c r="YP26" s="0"/>
+      <c r="YQ26" s="0"/>
+      <c r="YR26" s="0"/>
+      <c r="YS26" s="0"/>
+      <c r="YT26" s="0"/>
+      <c r="YU26" s="0"/>
+      <c r="YV26" s="0"/>
+      <c r="YW26" s="0"/>
+      <c r="YX26" s="0"/>
+      <c r="YY26" s="0"/>
+      <c r="YZ26" s="0"/>
+      <c r="ZA26" s="0"/>
+      <c r="ZB26" s="0"/>
+      <c r="ZC26" s="0"/>
+      <c r="ZD26" s="0"/>
+      <c r="ZE26" s="0"/>
+      <c r="ZF26" s="0"/>
+      <c r="ZG26" s="0"/>
+      <c r="ZH26" s="0"/>
+      <c r="ZI26" s="0"/>
+      <c r="ZJ26" s="0"/>
+      <c r="ZK26" s="0"/>
+      <c r="ZL26" s="0"/>
+      <c r="ZM26" s="0"/>
+      <c r="ZN26" s="0"/>
+      <c r="ZO26" s="0"/>
+      <c r="ZP26" s="0"/>
+      <c r="ZQ26" s="0"/>
+      <c r="ZR26" s="0"/>
+      <c r="ZS26" s="0"/>
+      <c r="ZT26" s="0"/>
+      <c r="ZU26" s="0"/>
+      <c r="ZV26" s="0"/>
+      <c r="ZW26" s="0"/>
+      <c r="ZX26" s="0"/>
+      <c r="ZY26" s="0"/>
+      <c r="ZZ26" s="0"/>
+      <c r="AAA26" s="0"/>
+      <c r="AAB26" s="0"/>
+      <c r="AAC26" s="0"/>
+      <c r="AAD26" s="0"/>
+      <c r="AAE26" s="0"/>
+      <c r="AAF26" s="0"/>
+      <c r="AAG26" s="0"/>
+      <c r="AAH26" s="0"/>
+      <c r="AAI26" s="0"/>
+      <c r="AAJ26" s="0"/>
+      <c r="AAK26" s="0"/>
+      <c r="AAL26" s="0"/>
+      <c r="AAM26" s="0"/>
+      <c r="AAN26" s="0"/>
+      <c r="AAO26" s="0"/>
+      <c r="AAP26" s="0"/>
+      <c r="AAQ26" s="0"/>
+      <c r="AAR26" s="0"/>
+      <c r="AAS26" s="0"/>
+      <c r="AAT26" s="0"/>
+      <c r="AAU26" s="0"/>
+      <c r="AAV26" s="0"/>
+      <c r="AAW26" s="0"/>
+      <c r="AAX26" s="0"/>
+      <c r="AAY26" s="0"/>
+      <c r="AAZ26" s="0"/>
+      <c r="ABA26" s="0"/>
+      <c r="ABB26" s="0"/>
+      <c r="ABC26" s="0"/>
+      <c r="ABD26" s="0"/>
+      <c r="ABE26" s="0"/>
+      <c r="ABF26" s="0"/>
+      <c r="ABG26" s="0"/>
+      <c r="ABH26" s="0"/>
+      <c r="ABI26" s="0"/>
+      <c r="ABJ26" s="0"/>
+      <c r="ABK26" s="0"/>
+      <c r="ABL26" s="0"/>
+      <c r="ABM26" s="0"/>
+      <c r="ABN26" s="0"/>
+      <c r="ABO26" s="0"/>
+      <c r="ABP26" s="0"/>
+      <c r="ABQ26" s="0"/>
+      <c r="ABR26" s="0"/>
+      <c r="ABS26" s="0"/>
+      <c r="ABT26" s="0"/>
+      <c r="ABU26" s="0"/>
+      <c r="ABV26" s="0"/>
+      <c r="ABW26" s="0"/>
+      <c r="ABX26" s="0"/>
+      <c r="ABY26" s="0"/>
+      <c r="ABZ26" s="0"/>
+      <c r="ACA26" s="0"/>
+      <c r="ACB26" s="0"/>
+      <c r="ACC26" s="0"/>
+      <c r="ACD26" s="0"/>
+      <c r="ACE26" s="0"/>
+      <c r="ACF26" s="0"/>
+      <c r="ACG26" s="0"/>
+      <c r="ACH26" s="0"/>
+      <c r="ACI26" s="0"/>
+      <c r="ACJ26" s="0"/>
+      <c r="ACK26" s="0"/>
+      <c r="ACL26" s="0"/>
+      <c r="ACM26" s="0"/>
+      <c r="ACN26" s="0"/>
+      <c r="ACO26" s="0"/>
+      <c r="ACP26" s="0"/>
+      <c r="ACQ26" s="0"/>
+      <c r="ACR26" s="0"/>
+      <c r="ACS26" s="0"/>
+      <c r="ACT26" s="0"/>
+      <c r="ACU26" s="0"/>
+      <c r="ACV26" s="0"/>
+      <c r="ACW26" s="0"/>
+      <c r="ACX26" s="0"/>
+      <c r="ACY26" s="0"/>
+      <c r="ACZ26" s="0"/>
+      <c r="ADA26" s="0"/>
+      <c r="ADB26" s="0"/>
+      <c r="ADC26" s="0"/>
+      <c r="ADD26" s="0"/>
+      <c r="ADE26" s="0"/>
+      <c r="ADF26" s="0"/>
+      <c r="ADG26" s="0"/>
+      <c r="ADH26" s="0"/>
+      <c r="ADI26" s="0"/>
+      <c r="ADJ26" s="0"/>
+      <c r="ADK26" s="0"/>
+      <c r="ADL26" s="0"/>
+      <c r="ADM26" s="0"/>
+      <c r="ADN26" s="0"/>
+      <c r="ADO26" s="0"/>
+      <c r="ADP26" s="0"/>
+      <c r="ADQ26" s="0"/>
+      <c r="ADR26" s="0"/>
+      <c r="ADS26" s="0"/>
+      <c r="ADT26" s="0"/>
+      <c r="ADU26" s="0"/>
+      <c r="ADV26" s="0"/>
+      <c r="ADW26" s="0"/>
+      <c r="ADX26" s="0"/>
+      <c r="ADY26" s="0"/>
+      <c r="ADZ26" s="0"/>
+      <c r="AEA26" s="0"/>
+      <c r="AEB26" s="0"/>
+      <c r="AEC26" s="0"/>
+      <c r="AED26" s="0"/>
+      <c r="AEE26" s="0"/>
+      <c r="AEF26" s="0"/>
+      <c r="AEG26" s="0"/>
+      <c r="AEH26" s="0"/>
+      <c r="AEI26" s="0"/>
+      <c r="AEJ26" s="0"/>
+      <c r="AEK26" s="0"/>
+      <c r="AEL26" s="0"/>
+      <c r="AEM26" s="0"/>
+      <c r="AEN26" s="0"/>
+      <c r="AEO26" s="0"/>
+      <c r="AEP26" s="0"/>
+      <c r="AEQ26" s="0"/>
+      <c r="AER26" s="0"/>
+      <c r="AES26" s="0"/>
+      <c r="AET26" s="0"/>
+      <c r="AEU26" s="0"/>
+      <c r="AEV26" s="0"/>
+      <c r="AEW26" s="0"/>
+      <c r="AEX26" s="0"/>
+      <c r="AEY26" s="0"/>
+      <c r="AEZ26" s="0"/>
+      <c r="AFA26" s="0"/>
+      <c r="AFB26" s="0"/>
+      <c r="AFC26" s="0"/>
+      <c r="AFD26" s="0"/>
+      <c r="AFE26" s="0"/>
+      <c r="AFF26" s="0"/>
+      <c r="AFG26" s="0"/>
+      <c r="AFH26" s="0"/>
+      <c r="AFI26" s="0"/>
+      <c r="AFJ26" s="0"/>
+      <c r="AFK26" s="0"/>
+      <c r="AFL26" s="0"/>
+      <c r="AFM26" s="0"/>
+      <c r="AFN26" s="0"/>
+      <c r="AFO26" s="0"/>
+      <c r="AFP26" s="0"/>
+      <c r="AFQ26" s="0"/>
+      <c r="AFR26" s="0"/>
+      <c r="AFS26" s="0"/>
+      <c r="AFT26" s="0"/>
+      <c r="AFU26" s="0"/>
+      <c r="AFV26" s="0"/>
+      <c r="AFW26" s="0"/>
+      <c r="AFX26" s="0"/>
+      <c r="AFY26" s="0"/>
+      <c r="AFZ26" s="0"/>
+      <c r="AGA26" s="0"/>
+      <c r="AGB26" s="0"/>
+      <c r="AGC26" s="0"/>
+      <c r="AGD26" s="0"/>
+      <c r="AGE26" s="0"/>
+      <c r="AGF26" s="0"/>
+      <c r="AGG26" s="0"/>
+      <c r="AGH26" s="0"/>
+      <c r="AGI26" s="0"/>
+      <c r="AGJ26" s="0"/>
+      <c r="AGK26" s="0"/>
+      <c r="AGL26" s="0"/>
+      <c r="AGM26" s="0"/>
+      <c r="AGN26" s="0"/>
+      <c r="AGO26" s="0"/>
+      <c r="AGP26" s="0"/>
+      <c r="AGQ26" s="0"/>
+      <c r="AGR26" s="0"/>
+      <c r="AGS26" s="0"/>
+      <c r="AGT26" s="0"/>
+      <c r="AGU26" s="0"/>
+      <c r="AGV26" s="0"/>
+      <c r="AGW26" s="0"/>
+      <c r="AGX26" s="0"/>
+      <c r="AGY26" s="0"/>
+      <c r="AGZ26" s="0"/>
+      <c r="AHA26" s="0"/>
+      <c r="AHB26" s="0"/>
+      <c r="AHC26" s="0"/>
+      <c r="AHD26" s="0"/>
+      <c r="AHE26" s="0"/>
+      <c r="AHF26" s="0"/>
+      <c r="AHG26" s="0"/>
+      <c r="AHH26" s="0"/>
+      <c r="AHI26" s="0"/>
+      <c r="AHJ26" s="0"/>
+      <c r="AHK26" s="0"/>
+      <c r="AHL26" s="0"/>
+      <c r="AHM26" s="0"/>
+      <c r="AHN26" s="0"/>
+      <c r="AHO26" s="0"/>
+      <c r="AHP26" s="0"/>
+      <c r="AHQ26" s="0"/>
+      <c r="AHR26" s="0"/>
+      <c r="AHS26" s="0"/>
+      <c r="AHT26" s="0"/>
+      <c r="AHU26" s="0"/>
+      <c r="AHV26" s="0"/>
+      <c r="AHW26" s="0"/>
+      <c r="AHX26" s="0"/>
+      <c r="AHY26" s="0"/>
+      <c r="AHZ26" s="0"/>
+      <c r="AIA26" s="0"/>
+      <c r="AIB26" s="0"/>
+      <c r="AIC26" s="0"/>
+      <c r="AID26" s="0"/>
+      <c r="AIE26" s="0"/>
+      <c r="AIF26" s="0"/>
+      <c r="AIG26" s="0"/>
+      <c r="AIH26" s="0"/>
+      <c r="AII26" s="0"/>
+      <c r="AIJ26" s="0"/>
+      <c r="AIK26" s="0"/>
+      <c r="AIL26" s="0"/>
+      <c r="AIM26" s="0"/>
+      <c r="AIN26" s="0"/>
+      <c r="AIO26" s="0"/>
+      <c r="AIP26" s="0"/>
+      <c r="AIQ26" s="0"/>
+      <c r="AIR26" s="0"/>
+      <c r="AIS26" s="0"/>
+      <c r="AIT26" s="0"/>
+      <c r="AIU26" s="0"/>
+      <c r="AIV26" s="0"/>
+      <c r="AIW26" s="0"/>
+      <c r="AIX26" s="0"/>
+      <c r="AIY26" s="0"/>
+      <c r="AIZ26" s="0"/>
+      <c r="AJA26" s="0"/>
+      <c r="AJB26" s="0"/>
+      <c r="AJC26" s="0"/>
+      <c r="AJD26" s="0"/>
+      <c r="AJE26" s="0"/>
+      <c r="AJF26" s="0"/>
+      <c r="AJG26" s="0"/>
+      <c r="AJH26" s="0"/>
+      <c r="AJI26" s="0"/>
+      <c r="AJJ26" s="0"/>
+      <c r="AJK26" s="0"/>
+      <c r="AJL26" s="0"/>
+      <c r="AJM26" s="0"/>
+      <c r="AJN26" s="0"/>
+      <c r="AJO26" s="0"/>
+      <c r="AJP26" s="0"/>
+      <c r="AJQ26" s="0"/>
+      <c r="AJR26" s="0"/>
+      <c r="AJS26" s="0"/>
+      <c r="AJT26" s="0"/>
+      <c r="AJU26" s="0"/>
+      <c r="AJV26" s="0"/>
+      <c r="AJW26" s="0"/>
+      <c r="AJX26" s="0"/>
+      <c r="AJY26" s="0"/>
+      <c r="AJZ26" s="0"/>
+      <c r="AKA26" s="0"/>
+      <c r="AKB26" s="0"/>
+      <c r="AKC26" s="0"/>
+      <c r="AKD26" s="0"/>
+      <c r="AKE26" s="0"/>
+      <c r="AKF26" s="0"/>
+      <c r="AKG26" s="0"/>
+      <c r="AKH26" s="0"/>
+      <c r="AKI26" s="0"/>
+      <c r="AKJ26" s="0"/>
+      <c r="AKK26" s="0"/>
+      <c r="AKL26" s="0"/>
+      <c r="AKM26" s="0"/>
+      <c r="AKN26" s="0"/>
+      <c r="AKO26" s="0"/>
+      <c r="AKP26" s="0"/>
+      <c r="AKQ26" s="0"/>
+      <c r="AKR26" s="0"/>
+      <c r="AKS26" s="0"/>
+      <c r="AKT26" s="0"/>
+      <c r="AKU26" s="0"/>
+      <c r="AKV26" s="0"/>
+      <c r="AKW26" s="0"/>
+      <c r="AKX26" s="0"/>
+      <c r="AKY26" s="0"/>
+      <c r="AKZ26" s="0"/>
+      <c r="ALA26" s="0"/>
+      <c r="ALB26" s="0"/>
+      <c r="ALC26" s="0"/>
+      <c r="ALD26" s="0"/>
+      <c r="ALE26" s="0"/>
+      <c r="ALF26" s="0"/>
+      <c r="ALG26" s="0"/>
+      <c r="ALH26" s="0"/>
+      <c r="ALI26" s="0"/>
+      <c r="ALJ26" s="0"/>
+      <c r="ALK26" s="0"/>
+      <c r="ALL26" s="0"/>
+      <c r="ALM26" s="0"/>
+      <c r="ALN26" s="0"/>
+      <c r="ALO26" s="0"/>
+      <c r="ALP26" s="0"/>
+      <c r="ALQ26" s="0"/>
+      <c r="ALR26" s="0"/>
+      <c r="ALS26" s="0"/>
+      <c r="ALT26" s="0"/>
+      <c r="ALU26" s="0"/>
+      <c r="ALV26" s="0"/>
+      <c r="ALW26" s="0"/>
+      <c r="ALX26" s="0"/>
+      <c r="ALY26" s="0"/>
+      <c r="ALZ26" s="0"/>
+      <c r="AMA26" s="0"/>
+      <c r="AMB26" s="0"/>
+      <c r="AMC26" s="0"/>
+      <c r="AMD26" s="0"/>
+      <c r="AME26" s="0"/>
+      <c r="AMF26" s="0"/>
+      <c r="AMG26" s="0"/>
+      <c r="AMH26" s="0"/>
+      <c r="AMI26" s="0"/>
+      <c r="AMJ26" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
